--- a/spreadsheets/pricing.xlsx
+++ b/spreadsheets/pricing.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="110">
   <si>
     <t>This document was exported from Numbers.  Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -301,16 +301,13 @@
     <t>Microcurrent Facial</t>
   </si>
   <si>
-    <t>$180</t>
-  </si>
-  <si>
     <t>Let's work those facial muscles! After cleansing and exfoliating, two probes pass an electric current through the face, training the facial muscles to appear more lifted and firm. A non-invasive facelift!</t>
   </si>
   <si>
     <t>Microcurrent (pkg of 6)</t>
   </si>
   <si>
-    <t>$150 each</t>
+    <t>150 each</t>
   </si>
   <si>
     <t>Rezenerate Nanofacial</t>
@@ -1670,7 +1667,7 @@
     </row>
     <row r="15">
       <c r="B15" t="s" s="3">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -1681,12 +1678,12 @@
         <v>5</v>
       </c>
       <c r="D16" t="s" s="5">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s" s="3">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -1697,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="s" s="5">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1938,7 +1935,7 @@
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E13" s="10">
         <v>10</v>
@@ -2159,7 +2156,7 @@
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E26" s="10">
         <v>15</v>
@@ -2176,7 +2173,7 @@
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E27" s="10">
         <v>15</v>
@@ -2193,7 +2190,7 @@
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E28" s="10">
         <v>10</v>
@@ -2651,23 +2648,23 @@
       </c>
       <c r="C5" s="8"/>
       <c r="D5" t="s" s="18">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E5" s="10">
         <v>55</v>
       </c>
       <c r="F5" t="s" s="11">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="8"/>
       <c r="B6" t="s" s="17">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" t="s" s="18">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E6" s="10">
         <v>55</v>
@@ -2677,33 +2674,33 @@
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="8"/>
       <c r="B7" t="s" s="17">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" t="s" s="18">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E7" s="10">
         <v>55</v>
       </c>
       <c r="F7" t="s" s="11">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" t="s" s="17">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" t="s" s="18">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E8" s="10">
         <v>75</v>
       </c>
       <c r="F8" t="s" s="11">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -2742,7 +2739,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="s" s="7">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s" s="7">
         <v>7</v>
@@ -2760,10 +2757,10 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="8"/>
       <c r="B2" t="s" s="11">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s" s="11">
         <v>100</v>
-      </c>
-      <c r="C2" t="s" s="11">
-        <v>101</v>
       </c>
       <c r="D2" s="10">
         <v>120</v>
@@ -2775,7 +2772,7 @@
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="8"/>
       <c r="B3" t="s" s="11">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="10">
@@ -2788,7 +2785,7 @@
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" t="s" s="11">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="10">
@@ -2801,7 +2798,7 @@
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" t="s" s="11">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="10">
@@ -2814,7 +2811,7 @@
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="8"/>
       <c r="B6" t="s" s="11">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="10">
@@ -2827,7 +2824,7 @@
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="8"/>
       <c r="B7" t="s" s="11">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="10">
@@ -2840,7 +2837,7 @@
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" t="s" s="11">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="10">
@@ -2853,7 +2850,7 @@
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="8"/>
       <c r="B9" t="s" s="11">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="10">
@@ -2866,7 +2863,7 @@
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="8"/>
       <c r="B10" t="s" s="11">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="10">

--- a/spreadsheets/pricing.xlsx
+++ b/spreadsheets/pricing.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="117">
   <si>
     <t>This document was exported from Numbers.  Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -144,25 +144,137 @@
     <t>FACIAL SERVICES</t>
   </si>
   <si>
+    <t>*NEW* Dermo-Booster Double Peel with Microcurrent</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">A high-performance resurfacing treatment designed to renew and refine the skin.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">&lt;br&gt;&lt;br&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">Beginning with a gentle fruit enzyme peel, followed by a powerful 30% triple-acid blend of glycolic, mandelic, and salicylic acids, this advanced formula stimulates collagen production, accelerates cell turnover, and visibly softens fine lines for a radiant glow.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">&lt;br&gt;&lt;br&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">Includes precise extractions, a calming hydrating ampoule, relaxing effleurage massage with aromatherapy, and a collagen + hyaluronic acid mask to leave skin smooth, plump, and radiant skin! 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">&lt;br&gt;&lt;br&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">This treatment also includes a targeted microcurrent session gently stimulating facial muscles to enhance contour and boost ATP, leaving skin visibly lifted, firmer, and toned.  
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">&lt;br&gt;&lt;br&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>Precision peel! Sculpted contour! “a no rest for Mona facial”</t>
+    </r>
+  </si>
+  <si>
+    <t>Dermo-Booster Double Peel with Microcurrent (pkg of 3)</t>
+  </si>
+  <si>
+    <t>285 each</t>
+  </si>
+  <si>
     <t>Detox Energie</t>
   </si>
   <si>
-    <t>Detox Energie is an intensive detoxifying energizing treatment that gives the skin a burst of energy, helping it defend itself against environmental stress which can accelerate skin aging.
-Detox Energie is a six step treatment of intense detoxifying, exfoliation, antipollution protection, oxygenation of the skin using Digi-Esthétique Massage rebalancing, and detox using ingredients such as Elderberry, Siberian Ginseng, Peptides, Marshmallow extract, Vitamin C, and Marine complex, leaving the skin energized and radiant!</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="14"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">Detox Energie is an intensive detoxifying energizing treatment that gives the skin a burst of energy, helping it defend itself against environmental stress which can accelerate skin aging. Detox Energie is a six step treatment of intense detoxifying, exfoliation, antipollution protection, oxygenation of the skin using Digi-Esthétique Massage rebalancing, and detox using ingredients such as Elderberry, Siberian Ginseng, Peptides, Marshmallow extract, Vitamin C, and Marine complex, leaving the skin energized and radiant!
+</t>
+    </r>
   </si>
   <si>
     <t>Organic Certified Radiance Treatment by Sothys Organics®</t>
   </si>
   <si>
-    <t>A Certified Organic and Vegan facial packed with the most effective ingredients obtained from organic farming and harvested by hand, such as Oleo-extract of honeysuckle,
-Birch Sap, Rasberry Seeds, Hawthorn Flower Water, and Alfalfa extract.
-This revitalizing facial is suitable for all skin types.</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="14"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>A Certified Organic and Vegan facial packed with the most effective ingredients obtained from organic farming and harvested by hand, such as Oleo-extract of honeysuckle, Birch Sap, Rasberry Seeds, Hawthorn Flower Water, and Alfalfa extract. This revitalizing facial is suitable for all skin types.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="14"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
   </si>
   <si>
     <t>European Facial</t>
   </si>
   <si>
-    <t>An introductory facial tailored to the individual's skin type and needs. To maintain a healthy and clear complexion, we use a customized selection of Sothys products -in a multi-step process- addressing the current need of your skin.</t>
+    <t>An introductory facial tailored to the individual's skin type and needs. To maintain a healthy and clear complexion, we use a customized selection of Sothys products in a multi-step process addressing the current needs of your skin.</t>
   </si>
   <si>
     <t>European Facial (pkg of 3)</t>
@@ -180,19 +292,19 @@
     <t>Mona's Glow Facial</t>
   </si>
   <si>
-    <t>A european facial adding Glysalac Peel for a deeper exfoliation followed by manual extractions and Mona's unique signature massage. Topping the treatment with a choice of luxurious, hydrating or soothing ampule to complete the glow.</t>
-  </si>
-  <si>
-    <t>Mona's Brightening Facial</t>
-  </si>
-  <si>
-    <t>A european facial with the addition of Sothys Lactic Acid Peel that resurfaces superficial lines and stimulates cell rejuvenation and brightening. Followed by a manual extraction and Mona's unique signature massage. Topping the treatment with a soothing ampule and Sothys W+ Brightening mask to complete this non-irritating acid treatment.</t>
+    <t>A European facial adding Glysalac Peel for a deeper exfoliation, followed by manual extractions and Mona's unique signature massage. Topping the treatment with a choice of luxurious, hydrating or soothing ampule to complete the glow.</t>
+  </si>
+  <si>
+    <t>Mona's Illuminating Facial</t>
+  </si>
+  <si>
+    <t>A European facial with the addition of Sothys Lactic Acid Peel that resurfaces superficial lines and stimulates cell rejuvenation and brightening. Followed by a manual extraction and Mona's unique signature massage. Topping the treatment with a soothing ampule and Sothys W+ Illuminating Mask to complete this non-irritating acid treatment.</t>
   </si>
   <si>
     <t>Bio-Élita Aqua Detox Charcoal Facial</t>
   </si>
   <si>
-    <t>A real detox and hydrating booster facial. A mask woven from cellulose and charcoal, deeply cleanses,purifies and detoxifies the skin by removing impurities, toxins and excess sebum while preserving the skin's hydrolipidic film. Best for dehydrated, demanding and sensitive skin.</t>
+    <t>A real detox and hydrating booster facial. A mask woven from cellulose and charcoal, deeply cleanses, purifies and detoxifies the skin by removing impurities, toxins and excess sebum while preserving the skin's hydrolipidic film. Best for dehydrated, demanding and sensitive skin.</t>
   </si>
   <si>
     <t>Perle de Caviar Bio Marine Facial (Face and Neck)</t>
@@ -255,7 +367,83 @@
     <t>Desciption</t>
   </si>
   <si>
-    <t>*NEW* Intraceuticals Oxygen Facial</t>
+    <t>*NEW* Radiance Renewal LED Therapy</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">Immerse your skin in the quiet luxury of advanced light technology. An enzymatic exfoliant gently refines texture, followed by an effleurage massage to relax and rejuvenate.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">&lt;br&gt;&lt;br&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">Red Light Therapy then awakens collagen, softens fine lines, and restores a luminous, youthful glow.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">&lt;br&gt;&lt;br&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">A bio-cellulose collagen anti-aging mask seals in nourishment, leaving skin refreshed, sculpted, and radiant. With no downtime and immediate luminosity, this results-driven ritual elevates any facial into a transformative experience.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">&lt;br&gt;&lt;br&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>LED add-on Treatment $55 (LED enhancement requires 20 extra minutes for optimal results)</t>
+    </r>
+  </si>
+  <si>
+    <t>Radiance Renewal LED Therapy (pkg of 3)</t>
+  </si>
+  <si>
+    <t>150 each</t>
+  </si>
+  <si>
+    <t>Intraceuticals Oxygen Facial</t>
   </si>
   <si>
     <t>235</t>
@@ -292,9 +480,6 @@
     <t>Microdermabrasion Facial</t>
   </si>
   <si>
-    <t>180</t>
-  </si>
-  <si>
     <t>European facial integrated into the Microdermabrasion treatment.</t>
   </si>
   <si>
@@ -305,9 +490,6 @@
   </si>
   <si>
     <t>Microcurrent (pkg of 6)</t>
-  </si>
-  <si>
-    <t>150 each</t>
   </si>
   <si>
     <t>Rezenerate Nanofacial</t>
@@ -374,7 +556,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -416,6 +598,11 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val=".AppleSystemUIFont"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="14"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="5">
@@ -473,7 +660,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -516,6 +703,9 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -525,8 +715,8 @@
     <xf numFmtId="0" fontId="6" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
@@ -562,6 +752,7 @@
       <rgbColor rgb="ff0000ff"/>
       <rgbColor rgb="ffaaaaaa"/>
       <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ff646464"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1651,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="B13" t="s" s="3">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -1662,12 +1853,12 @@
         <v>5</v>
       </c>
       <c r="D14" t="s" s="5">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s" s="3">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -1678,12 +1869,12 @@
         <v>5</v>
       </c>
       <c r="D16" t="s" s="5">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s" s="3">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -1694,7 +1885,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="s" s="5">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2263,10 +2454,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="6" width="14.5" style="12" customWidth="1"/>
+    <col min="1" max="5" width="14.5" style="12" customWidth="1"/>
+    <col min="6" max="6" width="62.5" style="12" customWidth="1"/>
     <col min="7" max="16384" width="14.5" style="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2290,17 +2482,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" ht="191.95" customHeight="1">
       <c r="A2" t="s" s="11">
         <v>42</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="10">
-        <v>185</v>
+        <v>305</v>
       </c>
       <c r="E2" s="10">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F2" t="s" s="13">
         <v>43</v>
@@ -2312,15 +2504,13 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="10">
-        <v>145</v>
+      <c r="D3" t="s" s="11">
+        <v>45</v>
       </c>
       <c r="E3" s="10">
-        <v>55</v>
-      </c>
-      <c r="F3" t="s" s="13">
-        <v>45</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="F3" s="14"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" t="s" s="11">
@@ -2329,12 +2519,12 @@
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="10">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="E4" s="10">
-        <v>55</v>
-      </c>
-      <c r="F4" t="s" s="11">
+        <v>75</v>
+      </c>
+      <c r="F4" t="s" s="13">
         <v>47</v>
       </c>
     </row>
@@ -2344,13 +2534,15 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
-      <c r="D5" t="s" s="11">
-        <v>49</v>
+      <c r="D5" s="10">
+        <v>145</v>
       </c>
       <c r="E5" s="10">
         <v>55</v>
       </c>
-      <c r="F5" s="8"/>
+      <c r="F5" t="s" s="13">
+        <v>49</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" t="s" s="11">
@@ -2358,13 +2550,15 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
-      <c r="D6" t="s" s="11">
-        <v>51</v>
+      <c r="D6" s="10">
+        <v>125</v>
       </c>
       <c r="E6" s="10">
         <v>55</v>
       </c>
-      <c r="F6" s="8"/>
+      <c r="F6" t="s" s="11">
+        <v>51</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" t="s" s="11">
@@ -2372,15 +2566,13 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
-      <c r="D7" s="10">
-        <v>205</v>
+      <c r="D7" t="s" s="11">
+        <v>53</v>
       </c>
       <c r="E7" s="10">
-        <v>75</v>
-      </c>
-      <c r="F7" t="s" s="11">
-        <v>53</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" t="s" s="11">
@@ -2388,15 +2580,13 @@
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
-      <c r="D8" s="10">
-        <v>215</v>
+      <c r="D8" t="s" s="11">
+        <v>55</v>
       </c>
       <c r="E8" s="10">
-        <v>75</v>
-      </c>
-      <c r="F8" t="s" s="11">
         <v>55</v>
       </c>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" t="s" s="11">
@@ -2405,10 +2595,10 @@
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="10">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="E9" s="10">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s" s="11">
         <v>57</v>
@@ -2421,12 +2611,12 @@
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="10">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E10" s="10">
-        <v>70</v>
-      </c>
-      <c r="F10" t="s" s="13">
+        <v>75</v>
+      </c>
+      <c r="F10" t="s" s="11">
         <v>59</v>
       </c>
     </row>
@@ -2437,12 +2627,12 @@
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="10">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="E11" s="10">
-        <v>30</v>
-      </c>
-      <c r="F11" t="s" s="13">
+        <v>60</v>
+      </c>
+      <c r="F11" t="s" s="11">
         <v>61</v>
       </c>
     </row>
@@ -2453,7 +2643,7 @@
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="10">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="E12" s="10">
         <v>70</v>
@@ -2469,10 +2659,10 @@
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="10">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="E13" s="10">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s" s="13">
         <v>65</v>
@@ -2485,10 +2675,10 @@
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="10">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="E14" s="10">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F14" t="s" s="13">
         <v>67</v>
@@ -2501,10 +2691,10 @@
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="10">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="E15" s="10">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s" s="13">
         <v>69</v>
@@ -2517,12 +2707,12 @@
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="10">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E16" s="10">
         <v>45</v>
       </c>
-      <c r="F16" t="s" s="11">
+      <c r="F16" t="s" s="13">
         <v>71</v>
       </c>
     </row>
@@ -2532,13 +2722,15 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
-      <c r="D17" t="s" s="11">
-        <v>73</v>
+      <c r="D17" s="10">
+        <v>125</v>
       </c>
       <c r="E17" s="10">
         <v>45</v>
       </c>
-      <c r="F17" s="8"/>
+      <c r="F17" t="s" s="13">
+        <v>73</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" t="s" s="11">
@@ -2547,12 +2739,42 @@
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="10">
+        <v>100</v>
+      </c>
+      <c r="E18" s="10">
+        <v>45</v>
+      </c>
+      <c r="F18" t="s" s="11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" t="s" s="11">
+        <v>76</v>
+      </c>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" t="s" s="11">
+        <v>77</v>
+      </c>
+      <c r="E19" s="10">
+        <v>45</v>
+      </c>
+      <c r="F19" s="8"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" t="s" s="11">
+        <v>78</v>
+      </c>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="10">
         <v>70</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E20" s="10">
         <v>15</v>
       </c>
-      <c r="F18" s="8"/>
+      <c r="F20" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2565,17 +2787,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="5" width="14.5" style="14" customWidth="1"/>
-    <col min="6" max="6" width="52.5625" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="14.5" style="14" customWidth="1"/>
+    <col min="1" max="5" width="14.5" style="15" customWidth="1"/>
+    <col min="6" max="6" width="52.5625" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="14.5" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="s" s="7">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s" s="7">
         <v>7</v>
@@ -2583,141 +2805,171 @@
       <c r="C1" t="s" s="7">
         <v>8</v>
       </c>
-      <c r="D1" t="s" s="15">
+      <c r="D1" t="s" s="16">
         <v>9</v>
       </c>
       <c r="E1" t="s" s="7">
         <v>10</v>
       </c>
       <c r="F1" t="s" s="7">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" ht="332.85" customHeight="1">
-      <c r="A2" s="16"/>
-      <c r="B2" t="s" s="17">
-        <v>78</v>
-      </c>
-      <c r="C2" s="16"/>
-      <c r="D2" t="s" s="18">
-        <v>79</v>
+      <c r="A2" s="17"/>
+      <c r="B2" t="s" s="18">
+        <v>82</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" t="s" s="19">
+        <v>83</v>
       </c>
       <c r="E2" s="10">
+        <v>55</v>
+      </c>
+      <c r="F2" t="s" s="13">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" ht="78.85" customHeight="1">
+      <c r="A3" s="17"/>
+      <c r="B3" t="s" s="18">
+        <v>85</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" t="s" s="19">
+        <v>86</v>
+      </c>
+      <c r="E3" s="10">
+        <v>55</v>
+      </c>
+      <c r="F3" s="14"/>
+    </row>
+    <row r="4" ht="332.85" customHeight="1">
+      <c r="A4" s="17"/>
+      <c r="B4" t="s" s="11">
+        <v>87</v>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" t="s" s="19">
+        <v>88</v>
+      </c>
+      <c r="E4" s="10">
         <v>60</v>
       </c>
-      <c r="F2" t="s" s="13">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="8"/>
-      <c r="B3" t="s" s="17">
-        <v>81</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" t="s" s="18">
-        <v>82</v>
-      </c>
-      <c r="E3" s="10">
-        <v>30</v>
-      </c>
-      <c r="F3" t="s" s="11">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" t="s" s="17">
-        <v>84</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" t="s" s="18">
-        <v>85</v>
-      </c>
-      <c r="E4" s="10">
-        <v>55</v>
-      </c>
-      <c r="F4" t="s" s="11">
-        <v>86</v>
+      <c r="F4" t="s" s="13">
+        <v>89</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" t="s" s="17">
-        <v>87</v>
+      <c r="B5" t="s" s="11">
+        <v>90</v>
       </c>
       <c r="C5" s="8"/>
-      <c r="D5" t="s" s="18">
-        <v>85</v>
+      <c r="D5" t="s" s="19">
+        <v>91</v>
       </c>
       <c r="E5" s="10">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s" s="11">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="8"/>
-      <c r="B6" t="s" s="17">
-        <v>89</v>
+      <c r="B6" t="s" s="11">
+        <v>93</v>
       </c>
       <c r="C6" s="8"/>
-      <c r="D6" t="s" s="18">
-        <v>90</v>
+      <c r="D6" t="s" s="19">
+        <v>83</v>
       </c>
       <c r="E6" s="10">
         <v>55</v>
       </c>
-      <c r="F6" s="8"/>
+      <c r="F6" t="s" s="11">
+        <v>94</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="8"/>
-      <c r="B7" t="s" s="17">
-        <v>91</v>
+      <c r="B7" t="s" s="11">
+        <v>95</v>
       </c>
       <c r="C7" s="8"/>
-      <c r="D7" t="s" s="18">
-        <v>92</v>
+      <c r="D7" t="s" s="19">
+        <v>83</v>
       </c>
       <c r="E7" s="10">
         <v>55</v>
       </c>
       <c r="F7" t="s" s="11">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="8"/>
-      <c r="B8" t="s" s="17">
-        <v>94</v>
+      <c r="B8" t="s" s="11">
+        <v>97</v>
       </c>
       <c r="C8" s="8"/>
-      <c r="D8" t="s" s="18">
-        <v>95</v>
+      <c r="D8" t="s" s="19">
+        <v>86</v>
       </c>
       <c r="E8" s="10">
-        <v>75</v>
-      </c>
-      <c r="F8" t="s" s="11">
-        <v>96</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="B9" t="s" s="11">
+        <v>98</v>
+      </c>
       <c r="C9" s="8"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" ht="13.65" customHeight="1">
+      <c r="D9" t="s" s="19">
+        <v>99</v>
+      </c>
+      <c r="E9" s="10">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="B10" t="s" s="11">
+        <v>101</v>
+      </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+      <c r="D10" t="s" s="19">
+        <v>102</v>
+      </c>
+      <c r="E10" s="10">
+        <v>75</v>
+      </c>
+      <c r="F10" t="s" s="11">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" ht="13.65" customHeight="1">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2733,13 +2985,13 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="5" width="14.5" style="20" customWidth="1"/>
-    <col min="6" max="16384" width="14.5" style="20" customWidth="1"/>
+    <col min="1" max="5" width="14.5" style="21" customWidth="1"/>
+    <col min="6" max="16384" width="14.5" style="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="s" s="7">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B1" t="s" s="7">
         <v>7</v>
@@ -2757,10 +3009,10 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="8"/>
       <c r="B2" t="s" s="11">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s" s="11">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D2" s="10">
         <v>120</v>
@@ -2772,7 +3024,7 @@
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="8"/>
       <c r="B3" t="s" s="11">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="10">
@@ -2785,7 +3037,7 @@
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" t="s" s="11">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="10">
@@ -2798,7 +3050,7 @@
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" t="s" s="11">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="10">
@@ -2811,7 +3063,7 @@
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="8"/>
       <c r="B6" t="s" s="11">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="10">
@@ -2824,7 +3076,7 @@
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="8"/>
       <c r="B7" t="s" s="11">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="10">
@@ -2837,7 +3089,7 @@
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" t="s" s="11">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="10">
@@ -2850,7 +3102,7 @@
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="8"/>
       <c r="B9" t="s" s="11">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="10">
@@ -2863,7 +3115,7 @@
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="8"/>
       <c r="B10" t="s" s="11">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="10">
@@ -2887,8 +3139,8 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="5" width="11.5" style="21" customWidth="1"/>
-    <col min="6" max="16384" width="11.5" style="21" customWidth="1"/>
+    <col min="1" max="5" width="11.5" style="22" customWidth="1"/>
+    <col min="6" max="16384" width="11.5" style="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.65" customHeight="1">

--- a/spreadsheets/pricing.xlsx
+++ b/spreadsheets/pricing.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="118">
   <si>
     <t>This document was exported from Numbers.  Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -144,7 +144,7 @@
     <t>FACIAL SERVICES</t>
   </si>
   <si>
-    <t>*NEW* Dermo-Booster Double Peel with Microcurrent</t>
+    <t>*NEW* Dermo-Booster Double Peel Treatment with Microcurrent</t>
   </si>
   <si>
     <r>
@@ -225,14 +225,14 @@
         <color indexed="8"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>Precision peel! Sculpted contour! “a no rest for Mona facial”</t>
+      <t>Precision peel! Sculpted contour! A no-rest-for-Mona facial!</t>
     </r>
   </si>
   <si>
-    <t>Dermo-Booster Double Peel with Microcurrent (pkg of 3)</t>
-  </si>
-  <si>
-    <t>285 each</t>
+    <t>Dermo-Booster Double Peel Treatment with Microcurrent (pkg of 3)</t>
+  </si>
+  <si>
+    <t>780 ($260 each)</t>
   </si>
   <si>
     <t>Detox Energie</t>
@@ -433,14 +433,14 @@
         <color indexed="8"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>LED add-on Treatment $55 (LED enhancement requires 20 extra minutes for optimal results)</t>
+      <t>&lt;b&gt;LED add-on Treatment $55 (LED enhancement requires 20 extra minutes for optimal results)&lt;/b&gt;</t>
     </r>
   </si>
   <si>
     <t>Radiance Renewal LED Therapy (pkg of 3)</t>
   </si>
   <si>
-    <t>150 each</t>
+    <t>450 ($150 each)</t>
   </si>
   <si>
     <t>Intraceuticals Oxygen Facial</t>
@@ -492,6 +492,9 @@
     <t>Microcurrent (pkg of 6)</t>
   </si>
   <si>
+    <t>150 each</t>
+  </si>
+  <si>
     <t>Rezenerate Nanofacial</t>
   </si>
   <si>
@@ -522,7 +525,7 @@
     <t>including lashes</t>
   </si>
   <si>
-    <t>Makeup (10 &amp; Under)</t>
+    <t>Makeup (Ages 10 &amp; Under)</t>
   </si>
   <si>
     <t>Lash Application (non-permanent)</t>
@@ -1858,7 +1861,7 @@
     </row>
     <row r="15">
       <c r="B15" t="s" s="3">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -1869,12 +1872,12 @@
         <v>5</v>
       </c>
       <c r="D16" t="s" s="5">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s" s="3">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -1885,7 +1888,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="s" s="5">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2916,7 +2919,7 @@
       </c>
       <c r="C8" s="8"/>
       <c r="D8" t="s" s="19">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E8" s="10">
         <v>55</v>
@@ -2926,33 +2929,33 @@
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="8"/>
       <c r="B9" t="s" s="11">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" t="s" s="19">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E9" s="10">
         <v>55</v>
       </c>
       <c r="F9" t="s" s="11">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="8"/>
       <c r="B10" t="s" s="11">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" t="s" s="19">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E10" s="10">
         <v>75</v>
       </c>
       <c r="F10" t="s" s="11">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -2991,7 +2994,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="s" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B1" t="s" s="7">
         <v>7</v>
@@ -3009,10 +3012,10 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="8"/>
       <c r="B2" t="s" s="11">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s" s="11">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D2" s="10">
         <v>120</v>
@@ -3024,7 +3027,7 @@
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="8"/>
       <c r="B3" t="s" s="11">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="10">
@@ -3037,7 +3040,7 @@
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" t="s" s="11">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="10">
@@ -3050,7 +3053,7 @@
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" t="s" s="11">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="10">
@@ -3063,7 +3066,7 @@
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="8"/>
       <c r="B6" t="s" s="11">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="10">
@@ -3076,7 +3079,7 @@
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="8"/>
       <c r="B7" t="s" s="11">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="10">
@@ -3089,7 +3092,7 @@
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" t="s" s="11">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="10">
@@ -3102,7 +3105,7 @@
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="8"/>
       <c r="B9" t="s" s="11">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="10">
@@ -3115,7 +3118,7 @@
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="8"/>
       <c r="B10" t="s" s="11">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="10">

--- a/spreadsheets/pricing.xlsx
+++ b/spreadsheets/pricing.xlsx
@@ -5,36 +5,17 @@
     <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="Export Summary" sheetId="1" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId5"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId6"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId7"/>
-    <sheet name="Sheet4" sheetId="5" r:id="rId8"/>
-    <sheet name="Sheet5" sheetId="6" r:id="rId9"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId6"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId7"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="118">
-  <si>
-    <t>This document was exported from Numbers.  Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
-  </si>
-  <si>
-    <t>Numbers Sheet Name</t>
-  </si>
-  <si>
-    <t>Numbers Table Name</t>
-  </si>
-  <si>
-    <t>Excel Worksheet Name</t>
-  </si>
-  <si>
-    <t>Sheet1</t>
-  </si>
-  <si>
-    <t>Table 1</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="103">
   <si>
     <t>WAX</t>
   </si>
@@ -136,9 +117,6 @@
   </si>
   <si>
     <t>At Mona's Makerie we use an all natural -no plastic fillers-cream wax for a thorough hair removal including  delicate and sensitive skin, leaving it smooth with no wax residue.our wax contains passion fruit extract Maracuja and  Theobroma Grandiflorum, a butter extracted from an Amazonian seed .</t>
-  </si>
-  <si>
-    <t>Sheet2</t>
   </si>
   <si>
     <t>FACIAL SERVICES</t>
@@ -149,7 +127,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
       </rPr>
@@ -158,7 +136,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
       </rPr>
@@ -167,7 +145,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
       </rPr>
@@ -176,7 +154,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
       </rPr>
@@ -185,7 +163,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
       </rPr>
@@ -194,7 +172,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
       </rPr>
@@ -203,7 +181,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
       </rPr>
@@ -212,7 +190,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
       </rPr>
@@ -221,7 +199,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
       </rPr>
@@ -229,10 +207,22 @@
     </r>
   </si>
   <si>
-    <t>Dermo-Booster Double Peel Treatment with Microcurrent (pkg of 3)</t>
+    <t>*NEW* Dermo-Booster Double Peel Treatment with Microcurrent (pkg of 3)</t>
   </si>
   <si>
     <t>780 ($260 each)</t>
+  </si>
+  <si>
+    <t>*NEW* PDRN Oxygen Facial</t>
+  </si>
+  <si>
+    <t>A customized peel followed by oxygen infusion of Intraceuticals’ PDRN Renewal Complex, featuring salmon-derived nucleotides, vitamins A, C &amp; E, antioxidant-rich green tea, and low-weight hyaluronic acid. Designed to intensify skin renewal while leaving the complexion visibly smoother, plumper, refreshed, and rejuvenated.</t>
+  </si>
+  <si>
+    <t>*NEW* Exosome+V Renewal Oxygen Facial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An advanced post-nano microneedling treatment featuring Intraceuticals’ Exosome+V Serum, infused with vegan biomimetic exosomes, vitamins A, C &amp; E, green tea extract, bioactive peptides, and low-weight hyaluronic acid to support skin communication, renewal, and long-term skin vitality. </t>
   </si>
   <si>
     <t>Detox Energie</t>
@@ -240,8 +230,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color indexed="14"/>
+        <sz val="9"/>
+        <color indexed="11"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Detox Energie is an intensive detoxifying energizing treatment that gives the skin a burst of energy, helping it defend itself against environmental stress which can accelerate skin aging. Detox Energie is a six step treatment of intense detoxifying, exfoliation, antipollution protection, oxygenation of the skin using Digi-Esthétique Massage rebalancing, and detox using ingredients such as Elderberry, Siberian Ginseng, Peptides, Marshmallow extract, Vitamin C, and Marine complex, leaving the skin energized and radiant!
@@ -254,16 +244,16 @@
   <si>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color indexed="14"/>
+        <sz val="9"/>
+        <color indexed="11"/>
         <rFont val="Arial"/>
       </rPr>
       <t>A Certified Organic and Vegan facial packed with the most effective ingredients obtained from organic farming and harvested by hand, such as Oleo-extract of honeysuckle, Birch Sap, Rasberry Seeds, Hawthorn Flower Water, and Alfalfa extract. This revitalizing facial is suitable for all skin types.</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color indexed="14"/>
+        <sz val="9"/>
+        <color indexed="11"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">
@@ -271,24 +261,6 @@
     </r>
   </si>
   <si>
-    <t>European Facial</t>
-  </si>
-  <si>
-    <t>An introductory facial tailored to the individual's skin type and needs. To maintain a healthy and clear complexion, we use a customized selection of Sothys products in a multi-step process addressing the current needs of your skin.</t>
-  </si>
-  <si>
-    <t>European Facial (pkg of 3)</t>
-  </si>
-  <si>
-    <t>115 each</t>
-  </si>
-  <si>
-    <t>European Facial (pkg of 5)</t>
-  </si>
-  <si>
-    <t>105 each</t>
-  </si>
-  <si>
     <t>Mona's Glow Facial</t>
   </si>
   <si>
@@ -331,34 +303,22 @@
     <t>A treatment filled with precious extracts of flowers, essential oils and fruit kernels to delicately recreate the optimum conditions of skin protection and effectively slow down the process of skin aging.</t>
   </si>
   <si>
-    <t>Thalassocaviar Facial</t>
-  </si>
-  <si>
-    <t>A Red Carpet Facial infused with nutrients and potent active ingredients massaged into the skin throughout the facial leaving your skin instantly plumped, hydrated and regenerated.</t>
-  </si>
-  <si>
     <t>Bacne Facial Treatment</t>
   </si>
   <si>
     <t>A back facial treatment will help to cleanse, exfoliate the skin, while treating any congestion and reveal smoother skin. A customized mask is applied to clarify and soften the skin while providing a deep detox treatment.</t>
   </si>
   <si>
-    <t>Teen Facial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A facial treatment focusing on the frequent problems of adolescent skin, perfect for ages &lt;b&gt;12-19&lt;/b&gt;. We begin with a thorough analysis and educational consult, followed by cleansing, exfoliation, and extractions. The service is topped off with a customized mask to balance and sooth the skin. &lt;i&gt;Parental consent must be signed before the service can be performed for minors&lt;/i&gt;. </t>
-  </si>
-  <si>
-    <t>Teen Facial (pkg of 3)</t>
-  </si>
-  <si>
-    <t>90 each</t>
+    <t>Teen Skin Renewal Treatment</t>
+  </si>
+  <si>
+    <t>Customized skin treatment featuring a gentle peel, thorough extractions, pressure point facial massage, LED light therapy, and a soothing, purifying mask leaving the skin fresh and balanced.</t>
+  </si>
+  <si>
+    <t>Teen Skin Renewal Treatment (pkg of 3)</t>
   </si>
   <si>
     <t>Add-on Peels</t>
-  </si>
-  <si>
-    <t>Sheet3</t>
   </si>
   <si>
     <t>DEVICES</t>
@@ -513,9 +473,6 @@
     <t>Microderm or peel added to a Rezenerate Nanofacial is a match made in Skin Heaven! You will leave with youthful and glowing skin.</t>
   </si>
   <si>
-    <t>Sheet4</t>
-  </si>
-  <si>
     <t>MAKEUP</t>
   </si>
   <si>
@@ -547,9 +504,6 @@
   </si>
   <si>
     <t>Halloween Makeup</t>
-  </si>
-  <si>
-    <t>Sheet5</t>
   </si>
 </sst>
 </file>
@@ -559,7 +513,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -568,23 +522,7 @@
     <font>
       <sz val="12"/>
       <color indexed="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
       <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <u val="single"/>
-      <sz val="12"/>
-      <color indexed="11"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="15"/>
@@ -603,12 +541,38 @@
       <name val=".AppleSystemUIFont"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Helvetica"/>
+    </font>
+    <font>
       <sz val="10"/>
-      <color indexed="14"/>
+      <color indexed="8"/>
+      <name val="Helvetica"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="11"/>
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -617,19 +581,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="9"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor indexed="10"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="13"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -644,16 +596,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="12"/>
+        <color indexed="9"/>
       </left>
       <right style="thin">
-        <color indexed="12"/>
+        <color indexed="9"/>
       </right>
       <top style="thin">
-        <color indexed="12"/>
+        <color indexed="9"/>
       </top>
       <bottom style="thin">
-        <color indexed="12"/>
+        <color indexed="9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,35 +615,20 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="6" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="7" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -700,31 +637,55 @@
     <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
@@ -750,9 +711,6 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ff5e88b1"/>
-      <rgbColor rgb="ffeef3f4"/>
-      <rgbColor rgb="ff0000ff"/>
       <rgbColor rgb="ffaaaaaa"/>
       <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ff646464"/>
@@ -1787,664 +1745,849 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I32"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="4" width="33.6016" customWidth="1"/>
+    <col min="1" max="9" width="14.5" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="14.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="50" customHeight="1">
-      <c r="B3" t="s" s="1">
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" t="s" s="2">
         <v>0</v>
       </c>
-      <c r="C3"/>
-      <c r="D3"/>
-    </row>
-    <row r="7">
-      <c r="B7" t="s" s="2">
+      <c r="B1" t="s" s="2">
         <v>1</v>
       </c>
-      <c r="C7" t="s" s="2">
+      <c r="C1" t="s" s="2">
         <v>2</v>
       </c>
-      <c r="D7" t="s" s="2">
+      <c r="D1" t="s" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="s" s="3">
+      <c r="E1" t="s" s="2">
         <v>4</v>
       </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="3"/>
+      <c r="B2" t="s" s="4">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="5">
+        <v>18</v>
+      </c>
+      <c r="E2" s="5">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" t="s" s="4">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="5">
+        <v>22</v>
+      </c>
+      <c r="E3" s="5">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="3"/>
+      <c r="B4" t="s" s="4">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="5">
+        <v>18</v>
+      </c>
+      <c r="E4" s="5">
+        <v>15</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="3"/>
+      <c r="B5" t="s" s="4">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="5">
+        <v>35</v>
+      </c>
+      <c r="E5" s="5">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="3"/>
+      <c r="B6" t="s" s="4">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="5">
+        <v>22</v>
+      </c>
+      <c r="E6" s="5">
+        <v>15</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="3"/>
+      <c r="B7" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="5">
+        <v>22</v>
+      </c>
+      <c r="E7" s="5">
+        <v>10</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="3"/>
+      <c r="B8" t="s" s="4">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="5">
+        <v>18</v>
+      </c>
+      <c r="E8" s="5">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="3"/>
+      <c r="B9" t="s" s="4">
+        <v>12</v>
+      </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="4"/>
-      <c r="C10" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="s" s="3">
-        <v>40</v>
+      <c r="D9" s="5">
+        <v>18</v>
+      </c>
+      <c r="E9" s="5">
+        <v>10</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="3"/>
+      <c r="B10" t="s" s="4">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="5">
+        <v>18</v>
+      </c>
+      <c r="E10" s="5">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="3"/>
+      <c r="B11" t="s" s="4">
+        <v>14</v>
       </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="4"/>
-      <c r="C12" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="D12" t="s" s="5">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="s" s="3">
-        <v>79</v>
+      <c r="D11" s="5">
+        <v>18</v>
+      </c>
+      <c r="E11" s="5">
+        <v>10</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="3"/>
+      <c r="B12" t="s" s="4">
+        <v>15</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="5">
+        <v>18</v>
+      </c>
+      <c r="E12" s="5">
+        <v>10</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="3"/>
+      <c r="B13" t="s" s="4">
+        <v>16</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="4"/>
-      <c r="C14" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="D14" t="s" s="5">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="s" s="3">
-        <v>105</v>
+      <c r="D13" s="5">
+        <v>18</v>
+      </c>
+      <c r="E13" s="5">
+        <v>10</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="3"/>
+      <c r="B14" t="s" s="4">
+        <v>17</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="5">
+        <v>45</v>
+      </c>
+      <c r="E14" s="5">
+        <v>20</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="3"/>
+      <c r="B15" t="s" s="4">
+        <v>18</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="4"/>
-      <c r="C16" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="D16" t="s" s="5">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="s" s="3">
-        <v>117</v>
+      <c r="D15" s="5">
+        <v>25</v>
+      </c>
+      <c r="E15" s="5">
+        <v>15</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="3"/>
+      <c r="B16" t="s" s="4">
+        <v>19</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="5">
+        <v>25</v>
+      </c>
+      <c r="E16" s="5">
+        <v>15</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="3"/>
+      <c r="B17" t="s" s="4">
+        <v>20</v>
       </c>
       <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="4"/>
-      <c r="C18" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="D18" t="s" s="5">
-        <v>117</v>
+      <c r="D17" s="5">
+        <v>18</v>
+      </c>
+      <c r="E17" s="5">
+        <v>10</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="3"/>
+      <c r="B18" t="s" s="4">
+        <v>21</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="5">
+        <v>95</v>
+      </c>
+      <c r="E18" s="5">
+        <v>20</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="3"/>
+      <c r="B19" t="s" s="4">
+        <v>22</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="5">
+        <v>65</v>
+      </c>
+      <c r="E19" s="5">
+        <v>15</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="3"/>
+      <c r="B20" t="s" s="4">
+        <v>23</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="5">
+        <v>45</v>
+      </c>
+      <c r="E20" s="5">
+        <v>15</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="3"/>
+      <c r="B21" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="5">
+        <v>18</v>
+      </c>
+      <c r="E21" s="5">
+        <v>15</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="3"/>
+      <c r="B22" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="5">
+        <v>45</v>
+      </c>
+      <c r="E22" s="5">
+        <v>15</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="3"/>
+      <c r="B23" t="s" s="4">
+        <v>26</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="5">
+        <v>60</v>
+      </c>
+      <c r="E23" s="5">
+        <v>20</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="3"/>
+      <c r="B24" t="s" s="4">
+        <v>27</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="5">
+        <v>80</v>
+      </c>
+      <c r="E24" s="5">
+        <v>30</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="3"/>
+      <c r="B25" t="s" s="4">
+        <v>28</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="5">
+        <v>50</v>
+      </c>
+      <c r="E25" s="5">
+        <v>30</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="3"/>
+      <c r="B26" t="s" s="4">
+        <v>29</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="5">
+        <v>22</v>
+      </c>
+      <c r="E26" s="5">
+        <v>15</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="3"/>
+      <c r="B27" t="s" s="4">
+        <v>30</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="5">
+        <v>22</v>
+      </c>
+      <c r="E27" s="5">
+        <v>15</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="3"/>
+      <c r="B28" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="5">
+        <v>18</v>
+      </c>
+      <c r="E28" s="5">
+        <v>10</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="5">
+        <v>30</v>
+      </c>
+      <c r="E29" s="5">
+        <v>15</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" ht="13.65" customHeight="1">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" t="s" s="6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" t="s" s="6">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B3:D3"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="D10" location="'Sheet1'!R1C1" tooltip="" display="Sheet1"/>
-    <hyperlink ref="D12" location="'Sheet2'!R1C1" tooltip="" display="Sheet2"/>
-    <hyperlink ref="D14" location="'Sheet3'!R1C1" tooltip="" display="Sheet3"/>
-    <hyperlink ref="D16" location="'Sheet4'!R1C1" tooltip="" display="Sheet4"/>
-    <hyperlink ref="D18" location="'Sheet5'!R1C1" tooltip="" display="Sheet5"/>
-  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="12.3" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="9" width="14.5" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="14.5" style="6" customWidth="1"/>
+    <col min="1" max="5" width="14.5" style="7" customWidth="1"/>
+    <col min="6" max="6" width="62.5" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="14.5" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" t="s" s="7">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s" s="7">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s" s="7">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s" s="7">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s" s="7">
-        <v>10</v>
-      </c>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="8"/>
-      <c r="B2" t="s" s="9">
-        <v>11</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="10">
-        <v>18</v>
-      </c>
-      <c r="E2" s="10">
-        <v>10</v>
-      </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="A1" t="s" s="8">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s" s="8">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="8">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="8">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="8">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" ht="191.95" customHeight="1">
+      <c r="A2" t="s" s="9">
+        <v>35</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="11">
+        <v>305</v>
+      </c>
+      <c r="E2" s="11">
+        <v>90</v>
+      </c>
+      <c r="F2" t="s" s="12">
+        <v>36</v>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="8"/>
-      <c r="B3" t="s" s="9">
-        <v>12</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="10">
-        <v>22</v>
-      </c>
-      <c r="E3" s="10">
-        <v>10</v>
-      </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
+      <c r="A3" t="s" s="9">
+        <v>37</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" t="s" s="9">
+        <v>38</v>
+      </c>
+      <c r="E3" s="11">
+        <v>90</v>
+      </c>
+      <c r="F3" s="13"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" t="s" s="9">
-        <v>13</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="10">
-        <v>18</v>
-      </c>
-      <c r="E4" s="10">
+      <c r="A4" t="s" s="9">
+        <v>39</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11">
+        <v>350</v>
+      </c>
+      <c r="E4" s="11">
+        <v>90</v>
+      </c>
+      <c r="F4" t="s" s="14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" t="s" s="15">
+        <v>41</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="11">
+        <v>425</v>
+      </c>
+      <c r="E5" s="11">
+        <v>90</v>
+      </c>
+      <c r="F5" t="s" s="14">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" t="s" s="9">
+        <v>43</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="11">
+        <v>185</v>
+      </c>
+      <c r="E6" s="11">
+        <v>60</v>
+      </c>
+      <c r="F6" t="s" s="12">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" t="s" s="6">
+        <v>45</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="11">
+        <v>145</v>
+      </c>
+      <c r="E7" s="11">
+        <v>55</v>
+      </c>
+      <c r="F7" t="s" s="12">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" t="s" s="6">
+        <v>47</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11">
+        <v>205</v>
+      </c>
+      <c r="E8" s="11">
+        <v>60</v>
+      </c>
+      <c r="F8" t="s" s="9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" t="s" s="6">
+        <v>49</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="11">
+        <v>215</v>
+      </c>
+      <c r="E9" s="11">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s" s="9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" t="s" s="6">
+        <v>51</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="11">
+        <v>175</v>
+      </c>
+      <c r="E10" s="11">
+        <v>60</v>
+      </c>
+      <c r="F10" t="s" s="9">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" t="s" s="6">
+        <v>53</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="11">
+        <v>220</v>
+      </c>
+      <c r="E11" s="11">
+        <v>70</v>
+      </c>
+      <c r="F11" t="s" s="12">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" t="s" s="6">
+        <v>55</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11">
+        <v>85</v>
+      </c>
+      <c r="E12" s="11">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s" s="12">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" t="s" s="6">
+        <v>57</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="11">
+        <v>250</v>
+      </c>
+      <c r="E13" s="11">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s" s="12">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" t="s" s="6">
+        <v>59</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="11">
+        <v>155</v>
+      </c>
+      <c r="E14" s="11">
+        <v>60</v>
+      </c>
+      <c r="F14" t="s" s="12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" t="s" s="6">
+        <v>61</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="11">
+        <v>125</v>
+      </c>
+      <c r="E15" s="11">
+        <v>45</v>
+      </c>
+      <c r="F15" t="s" s="12">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" t="s" s="6">
+        <v>63</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11">
+        <v>185</v>
+      </c>
+      <c r="E16" s="11">
+        <v>45</v>
+      </c>
+      <c r="F16" t="s" s="9">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" t="s" s="6">
+        <v>65</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="11">
+        <v>525</v>
+      </c>
+      <c r="E17" s="11">
+        <v>45</v>
+      </c>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" t="s" s="6">
+        <v>66</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="11">
+        <v>70</v>
+      </c>
+      <c r="E18" s="11">
         <v>15</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="8"/>
-      <c r="B5" t="s" s="9">
-        <v>14</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="10">
-        <v>35</v>
-      </c>
-      <c r="E5" s="10">
-        <v>15</v>
-      </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" t="s" s="9">
-        <v>15</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="10">
-        <v>22</v>
-      </c>
-      <c r="E6" s="10">
-        <v>15</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" t="s" s="9">
-        <v>16</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="10">
-        <v>22</v>
-      </c>
-      <c r="E7" s="10">
-        <v>10</v>
-      </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" t="s" s="9">
-        <v>17</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="10">
-        <v>18</v>
-      </c>
-      <c r="E8" s="10">
-        <v>15</v>
-      </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" t="s" s="9">
-        <v>18</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="10">
-        <v>18</v>
-      </c>
-      <c r="E9" s="10">
-        <v>10</v>
-      </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="8"/>
-      <c r="B10" t="s" s="9">
-        <v>19</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="10">
-        <v>18</v>
-      </c>
-      <c r="E10" s="10">
-        <v>10</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="8"/>
-      <c r="B11" t="s" s="9">
-        <v>20</v>
-      </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="10">
-        <v>18</v>
-      </c>
-      <c r="E11" s="10">
-        <v>10</v>
-      </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="8"/>
-      <c r="B12" t="s" s="9">
-        <v>21</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="10">
-        <v>18</v>
-      </c>
-      <c r="E12" s="10">
-        <v>10</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="8"/>
-      <c r="B13" t="s" s="9">
-        <v>22</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="10">
-        <v>18</v>
-      </c>
-      <c r="E13" s="10">
-        <v>10</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="8"/>
-      <c r="B14" t="s" s="9">
-        <v>23</v>
-      </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="10">
-        <v>45</v>
-      </c>
-      <c r="E14" s="10">
-        <v>20</v>
-      </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="8"/>
-      <c r="B15" t="s" s="9">
-        <v>24</v>
-      </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="10">
-        <v>25</v>
-      </c>
-      <c r="E15" s="10">
-        <v>15</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" t="s" s="9">
-        <v>25</v>
-      </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="10">
-        <v>25</v>
-      </c>
-      <c r="E16" s="10">
-        <v>15</v>
-      </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" t="s" s="9">
-        <v>26</v>
-      </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="10">
-        <v>18</v>
-      </c>
-      <c r="E17" s="10">
-        <v>10</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" t="s" s="9">
-        <v>27</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="10">
-        <v>95</v>
-      </c>
-      <c r="E18" s="10">
-        <v>20</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" t="s" s="9">
-        <v>28</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="10">
-        <v>65</v>
-      </c>
-      <c r="E19" s="10">
-        <v>15</v>
-      </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" t="s" s="9">
-        <v>29</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="10">
-        <v>45</v>
-      </c>
-      <c r="E20" s="10">
-        <v>15</v>
-      </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" t="s" s="9">
-        <v>30</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="10">
-        <v>18</v>
-      </c>
-      <c r="E21" s="10">
-        <v>15</v>
-      </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="8"/>
-      <c r="B22" t="s" s="9">
-        <v>31</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="10">
-        <v>45</v>
-      </c>
-      <c r="E22" s="10">
-        <v>15</v>
-      </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="8"/>
-      <c r="B23" t="s" s="9">
-        <v>32</v>
-      </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="10">
-        <v>60</v>
-      </c>
-      <c r="E23" s="10">
-        <v>20</v>
-      </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="8"/>
-      <c r="B24" t="s" s="9">
-        <v>33</v>
-      </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="10">
-        <v>80</v>
-      </c>
-      <c r="E24" s="10">
-        <v>30</v>
-      </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="8"/>
-      <c r="B25" t="s" s="9">
-        <v>34</v>
-      </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="10">
-        <v>50</v>
-      </c>
-      <c r="E25" s="10">
-        <v>30</v>
-      </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="8"/>
-      <c r="B26" t="s" s="9">
-        <v>35</v>
-      </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="10">
-        <v>22</v>
-      </c>
-      <c r="E26" s="10">
-        <v>15</v>
-      </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="8"/>
-      <c r="B27" t="s" s="9">
-        <v>36</v>
-      </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="10">
-        <v>22</v>
-      </c>
-      <c r="E27" s="10">
-        <v>15</v>
-      </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="8"/>
-      <c r="B28" t="s" s="9">
-        <v>37</v>
-      </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="10">
-        <v>18</v>
-      </c>
-      <c r="E28" s="10">
-        <v>10</v>
-      </c>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="10">
-        <v>30</v>
-      </c>
-      <c r="E29" s="10">
-        <v>15</v>
-      </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" ht="13.65" customHeight="1">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" t="s" s="11">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" t="s" s="11">
-        <v>39</v>
-      </c>
+      <c r="F18" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2457,327 +2600,189 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="5" width="14.5" style="12" customWidth="1"/>
-    <col min="6" max="6" width="62.5" style="12" customWidth="1"/>
-    <col min="7" max="16384" width="14.5" style="12" customWidth="1"/>
+    <col min="1" max="5" width="14.5" style="16" customWidth="1"/>
+    <col min="6" max="6" width="52.5625" style="16" customWidth="1"/>
+    <col min="7" max="16384" width="14.5" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" t="s" s="7">
-        <v>41</v>
-      </c>
-      <c r="B1" t="s" s="7">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s" s="7">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s" s="7">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s" s="7">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" ht="191.95" customHeight="1">
-      <c r="A2" t="s" s="11">
-        <v>42</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="10">
-        <v>305</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="A1" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B1" t="s" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="17">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" ht="332.85" customHeight="1">
+      <c r="A2" s="18"/>
+      <c r="B2" t="s" s="19">
+        <v>69</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" t="s" s="20">
+        <v>70</v>
+      </c>
+      <c r="E2" s="5">
+        <v>55</v>
+      </c>
+      <c r="F2" t="s" s="21">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" ht="78.85" customHeight="1">
+      <c r="A3" s="18"/>
+      <c r="B3" t="s" s="19">
+        <v>72</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" t="s" s="20">
+        <v>73</v>
+      </c>
+      <c r="E3" s="5">
+        <v>55</v>
+      </c>
+      <c r="F3" s="22"/>
+    </row>
+    <row r="4" ht="332.85" customHeight="1">
+      <c r="A4" s="18"/>
+      <c r="B4" t="s" s="6">
+        <v>74</v>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" t="s" s="20">
+        <v>75</v>
+      </c>
+      <c r="E4" s="5">
+        <v>60</v>
+      </c>
+      <c r="F4" t="s" s="21">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="3"/>
+      <c r="B5" t="s" s="6">
+        <v>77</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" t="s" s="20">
+        <v>78</v>
+      </c>
+      <c r="E5" s="5">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s" s="6">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="3"/>
+      <c r="B6" t="s" s="6">
+        <v>80</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" t="s" s="20">
+        <v>70</v>
+      </c>
+      <c r="E6" s="5">
+        <v>55</v>
+      </c>
+      <c r="F6" t="s" s="6">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="3"/>
+      <c r="B7" t="s" s="6">
+        <v>82</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" t="s" s="20">
+        <v>70</v>
+      </c>
+      <c r="E7" s="5">
+        <v>55</v>
+      </c>
+      <c r="F7" t="s" s="6">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="3"/>
+      <c r="B8" t="s" s="6">
+        <v>84</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" t="s" s="20">
+        <v>85</v>
+      </c>
+      <c r="E8" s="5">
+        <v>55</v>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="3"/>
+      <c r="B9" t="s" s="6">
+        <v>86</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" t="s" s="20">
+        <v>87</v>
+      </c>
+      <c r="E9" s="5">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s" s="6">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="3"/>
+      <c r="B10" t="s" s="6">
+        <v>89</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" t="s" s="20">
         <v>90</v>
       </c>
-      <c r="F2" t="s" s="13">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" t="s" s="11">
-        <v>44</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" t="s" s="11">
-        <v>45</v>
-      </c>
-      <c r="E3" s="10">
-        <v>90</v>
-      </c>
-      <c r="F3" s="14"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" t="s" s="11">
-        <v>46</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="10">
-        <v>185</v>
-      </c>
-      <c r="E4" s="10">
+      <c r="E10" s="5">
         <v>75</v>
       </c>
-      <c r="F4" t="s" s="13">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" t="s" s="11">
-        <v>48</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="10">
-        <v>145</v>
-      </c>
-      <c r="E5" s="10">
-        <v>55</v>
-      </c>
-      <c r="F5" t="s" s="13">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" t="s" s="11">
-        <v>50</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="10">
-        <v>125</v>
-      </c>
-      <c r="E6" s="10">
-        <v>55</v>
-      </c>
-      <c r="F6" t="s" s="11">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" t="s" s="11">
-        <v>52</v>
-      </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" t="s" s="11">
-        <v>53</v>
-      </c>
-      <c r="E7" s="10">
-        <v>55</v>
-      </c>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" t="s" s="11">
-        <v>54</v>
-      </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" t="s" s="11">
-        <v>55</v>
-      </c>
-      <c r="E8" s="10">
-        <v>55</v>
-      </c>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" t="s" s="11">
-        <v>56</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="10">
-        <v>205</v>
-      </c>
-      <c r="E9" s="10">
-        <v>75</v>
-      </c>
-      <c r="F9" t="s" s="11">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" t="s" s="11">
-        <v>58</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="10">
-        <v>215</v>
-      </c>
-      <c r="E10" s="10">
-        <v>75</v>
-      </c>
-      <c r="F10" t="s" s="11">
-        <v>59</v>
+      <c r="F10" t="s" s="6">
+        <v>91</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" t="s" s="11">
-        <v>60</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="10">
-        <v>175</v>
-      </c>
-      <c r="E11" s="10">
-        <v>60</v>
-      </c>
-      <c r="F11" t="s" s="11">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" t="s" s="11">
-        <v>62</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="10">
-        <v>220</v>
-      </c>
-      <c r="E12" s="10">
-        <v>70</v>
-      </c>
-      <c r="F12" t="s" s="13">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" t="s" s="11">
-        <v>64</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="10">
-        <v>85</v>
-      </c>
-      <c r="E13" s="10">
-        <v>30</v>
-      </c>
-      <c r="F13" t="s" s="13">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" t="s" s="11">
-        <v>66</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="10">
-        <v>250</v>
-      </c>
-      <c r="E14" s="10">
-        <v>70</v>
-      </c>
-      <c r="F14" t="s" s="13">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" t="s" s="11">
-        <v>68</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="10">
-        <v>155</v>
-      </c>
-      <c r="E15" s="10">
-        <v>60</v>
-      </c>
-      <c r="F15" t="s" s="13">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" t="s" s="11">
-        <v>70</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="10">
-        <v>125</v>
-      </c>
-      <c r="E16" s="10">
-        <v>45</v>
-      </c>
-      <c r="F16" t="s" s="13">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" t="s" s="11">
-        <v>72</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="10">
-        <v>125</v>
-      </c>
-      <c r="E17" s="10">
-        <v>45</v>
-      </c>
-      <c r="F17" t="s" s="13">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" t="s" s="11">
-        <v>74</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="10">
-        <v>100</v>
-      </c>
-      <c r="E18" s="10">
-        <v>45</v>
-      </c>
-      <c r="F18" t="s" s="11">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" t="s" s="11">
-        <v>76</v>
-      </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" t="s" s="11">
-        <v>77</v>
-      </c>
-      <c r="E19" s="10">
-        <v>45</v>
-      </c>
-      <c r="F19" s="8"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" t="s" s="11">
-        <v>78</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="10">
-        <v>70</v>
-      </c>
-      <c r="E20" s="10">
-        <v>15</v>
-      </c>
-      <c r="F20" s="8"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" ht="13.65" customHeight="1">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2790,189 +2795,148 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="5" width="14.5" style="15" customWidth="1"/>
-    <col min="6" max="6" width="52.5625" style="15" customWidth="1"/>
-    <col min="7" max="16384" width="14.5" style="15" customWidth="1"/>
+    <col min="1" max="5" width="14.5" style="24" customWidth="1"/>
+    <col min="6" max="16384" width="14.5" style="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" t="s" s="7">
+      <c r="A1" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="3"/>
+      <c r="B2" t="s" s="6">
+        <v>93</v>
+      </c>
+      <c r="C2" t="s" s="6">
+        <v>94</v>
+      </c>
+      <c r="D2" s="5">
+        <v>120</v>
+      </c>
+      <c r="E2" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" t="s" s="6">
+        <v>95</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="5">
         <v>80</v>
       </c>
-      <c r="B1" t="s" s="7">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s" s="7">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s" s="16">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s" s="7">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s" s="7">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" ht="332.85" customHeight="1">
-      <c r="A2" s="17"/>
-      <c r="B2" t="s" s="18">
-        <v>82</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="D2" t="s" s="19">
-        <v>83</v>
-      </c>
-      <c r="E2" s="10">
-        <v>55</v>
-      </c>
-      <c r="F2" t="s" s="13">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" ht="78.85" customHeight="1">
-      <c r="A3" s="17"/>
-      <c r="B3" t="s" s="18">
-        <v>85</v>
-      </c>
-      <c r="C3" s="17"/>
-      <c r="D3" t="s" s="19">
-        <v>86</v>
-      </c>
-      <c r="E3" s="10">
-        <v>55</v>
-      </c>
-      <c r="F3" s="14"/>
-    </row>
-    <row r="4" ht="332.85" customHeight="1">
-      <c r="A4" s="17"/>
-      <c r="B4" t="s" s="11">
-        <v>87</v>
-      </c>
-      <c r="C4" s="17"/>
-      <c r="D4" t="s" s="19">
-        <v>88</v>
-      </c>
-      <c r="E4" s="10">
+      <c r="E3" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="3"/>
+      <c r="B4" t="s" s="6">
+        <v>96</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="5">
+        <v>30</v>
+      </c>
+      <c r="E4" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="3"/>
+      <c r="B5" t="s" s="6">
+        <v>97</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="5">
+        <v>295</v>
+      </c>
+      <c r="E5" s="5">
         <v>60</v>
       </c>
-      <c r="F4" t="s" s="13">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="8"/>
-      <c r="B5" t="s" s="11">
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="3"/>
+      <c r="B6" t="s" s="6">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="5">
+        <v>300</v>
+      </c>
+      <c r="E6" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="3"/>
+      <c r="B7" t="s" s="6">
+        <v>99</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="5">
+        <v>150</v>
+      </c>
+      <c r="E7" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="3"/>
+      <c r="B8" t="s" s="6">
+        <v>100</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="5">
+        <v>225</v>
+      </c>
+      <c r="E8" s="5">
         <v>90</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" t="s" s="19">
-        <v>91</v>
-      </c>
-      <c r="E5" s="10">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s" s="11">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" t="s" s="11">
-        <v>93</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" t="s" s="19">
-        <v>83</v>
-      </c>
-      <c r="E6" s="10">
-        <v>55</v>
-      </c>
-      <c r="F6" t="s" s="11">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" t="s" s="11">
-        <v>95</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" t="s" s="19">
-        <v>83</v>
-      </c>
-      <c r="E7" s="10">
-        <v>55</v>
-      </c>
-      <c r="F7" t="s" s="11">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" t="s" s="11">
-        <v>97</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" t="s" s="19">
-        <v>98</v>
-      </c>
-      <c r="E8" s="10">
-        <v>55</v>
-      </c>
-      <c r="F8" s="8"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" t="s" s="11">
-        <v>99</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" t="s" s="19">
-        <v>100</v>
-      </c>
-      <c r="E9" s="10">
-        <v>55</v>
-      </c>
-      <c r="F9" t="s" s="11">
+      <c r="A9" s="3"/>
+      <c r="B9" t="s" s="6">
         <v>101</v>
       </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="5">
+        <v>325</v>
+      </c>
+      <c r="E9" s="5">
+        <v>120</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="8"/>
-      <c r="B10" t="s" s="11">
+      <c r="A10" s="3"/>
+      <c r="B10" t="s" s="6">
         <v>102</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" t="s" s="19">
-        <v>103</v>
-      </c>
-      <c r="E10" s="10">
-        <v>75</v>
-      </c>
-      <c r="F10" t="s" s="11">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-    </row>
-    <row r="12" ht="13.65" customHeight="1">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="5">
+        <v>150</v>
+      </c>
+      <c r="E10" s="5">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2986,235 +2950,81 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col min="1" max="5" width="14.5" style="21" customWidth="1"/>
-    <col min="6" max="16384" width="14.5" style="21" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" t="s" s="7">
-        <v>106</v>
-      </c>
-      <c r="B1" t="s" s="7">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s" s="7">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s" s="7">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="8"/>
-      <c r="B2" t="s" s="11">
-        <v>107</v>
-      </c>
-      <c r="C2" t="s" s="11">
-        <v>108</v>
-      </c>
-      <c r="D2" s="10">
-        <v>120</v>
-      </c>
-      <c r="E2" s="10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="8"/>
-      <c r="B3" t="s" s="11">
-        <v>109</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="10">
-        <v>80</v>
-      </c>
-      <c r="E3" s="10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" t="s" s="11">
-        <v>110</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="10">
-        <v>30</v>
-      </c>
-      <c r="E4" s="10">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="8"/>
-      <c r="B5" t="s" s="11">
-        <v>111</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="10">
-        <v>295</v>
-      </c>
-      <c r="E5" s="10">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" t="s" s="11">
-        <v>112</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="10">
-        <v>300</v>
-      </c>
-      <c r="E6" s="10">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" t="s" s="11">
-        <v>113</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="10">
-        <v>150</v>
-      </c>
-      <c r="E7" s="10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" t="s" s="11">
-        <v>114</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="10">
-        <v>225</v>
-      </c>
-      <c r="E8" s="10">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" t="s" s="11">
-        <v>115</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="10">
-        <v>325</v>
-      </c>
-      <c r="E9" s="10">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="8"/>
-      <c r="B10" t="s" s="11">
-        <v>116</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="10">
-        <v>150</v>
-      </c>
-      <c r="E10" s="10">
-        <v>60</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
-  <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="5" width="11.5" style="22" customWidth="1"/>
-    <col min="6" max="16384" width="11.5" style="22" customWidth="1"/>
+    <col min="1" max="5" width="11.5" style="25" customWidth="1"/>
+    <col min="6" max="16384" width="11.5" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.65" customHeight="1">
-      <c r="A1" s="8"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" ht="13.65" customHeight="1">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" ht="13.65" customHeight="1">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
     </row>
     <row r="4" ht="13.65" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
     </row>
     <row r="5" ht="13.65" customHeight="1">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
     </row>
     <row r="6" ht="13.65" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
     </row>
     <row r="7" ht="13.65" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
     </row>
     <row r="8" ht="13.65" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" ht="13.65" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" ht="13.65" customHeight="1">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/spreadsheets/pricing.xlsx
+++ b/spreadsheets/pricing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="101">
   <si>
     <t>WAX</t>
   </si>
@@ -225,6 +225,18 @@
     <t xml:space="preserve">An advanced post-nano microneedling treatment featuring Intraceuticals’ Exosome+V Serum, infused with vegan biomimetic exosomes, vitamins A, C &amp; E, green tea extract, bioactive peptides, and low-weight hyaluronic acid to support skin communication, renewal, and long-term skin vitality. </t>
   </si>
   <si>
+    <t>Mona's Glow Facial</t>
+  </si>
+  <si>
+    <t>A European facial adding Glysalac Peel for a deeper exfoliation, followed by manual extractions and Mona's unique signature massage. Topping the treatment with a choice of luxurious, hydrating or soothing ampule to complete the glow.</t>
+  </si>
+  <si>
+    <t>Mona's Illuminating Facial</t>
+  </si>
+  <si>
+    <t>A European facial with the addition of Sothys Lactic Acid Peel that resurfaces superficial lines and stimulates cell rejuvenation and brightening. Followed by a manual extraction and Mona's unique signature massage. Topping the treatment with a soothing ampule and Sothys W+ Illuminating Mask to complete this non-irritating acid treatment.</t>
+  </si>
+  <si>
     <t>Detox Energie</t>
   </si>
   <si>
@@ -261,18 +273,6 @@
     </r>
   </si>
   <si>
-    <t>Mona's Glow Facial</t>
-  </si>
-  <si>
-    <t>A European facial adding Glysalac Peel for a deeper exfoliation, followed by manual extractions and Mona's unique signature massage. Topping the treatment with a choice of luxurious, hydrating or soothing ampule to complete the glow.</t>
-  </si>
-  <si>
-    <t>Mona's Illuminating Facial</t>
-  </si>
-  <si>
-    <t>A European facial with the addition of Sothys Lactic Acid Peel that resurfaces superficial lines and stimulates cell rejuvenation and brightening. Followed by a manual extraction and Mona's unique signature massage. Topping the treatment with a soothing ampule and Sothys W+ Illuminating Mask to complete this non-irritating acid treatment.</t>
-  </si>
-  <si>
     <t>Bio-Élita Aqua Detox Charcoal Facial</t>
   </si>
   <si>
@@ -309,13 +309,16 @@
     <t>A back facial treatment will help to cleanse, exfoliate the skin, while treating any congestion and reveal smoother skin. A customized mask is applied to clarify and soften the skin while providing a deep detox treatment.</t>
   </si>
   <si>
-    <t>Teen Skin Renewal Treatment</t>
+    <t>Teen Skin Treatment</t>
   </si>
   <si>
     <t>Customized skin treatment featuring a gentle peel, thorough extractions, pressure point facial massage, LED light therapy, and a soothing, purifying mask leaving the skin fresh and balanced.</t>
   </si>
   <si>
-    <t>Teen Skin Renewal Treatment (pkg of 3)</t>
+    <t>Teen Skin Treatment (pkg of 3)</t>
+  </si>
+  <si>
+    <t>525 ($175 each)</t>
   </si>
   <si>
     <t>Add-on Peels</t>
@@ -428,15 +431,6 @@
 &lt;li&gt;&lt;b&gt;Rejuvenate moisture rich lip mask &lt;b&gt;| $15&lt;/b&gt;&lt;/li&gt;</t>
   </si>
   <si>
-    <t>Microdermabrasion</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>Microdermabrasion is a non-invasive resurfacing treatment. Select between Crystal or Diamond tip to suction impurities removing superifical layers of dry, congested skin cells, fine lines, uneven pigmentation, or clogged pores, unveiling smoother, healthier and younger skin.</t>
-  </si>
-  <si>
     <t>Microdermabrasion Facial</t>
   </si>
   <si>
@@ -452,7 +446,7 @@
     <t>Microcurrent (pkg of 6)</t>
   </si>
   <si>
-    <t>150 each</t>
+    <t>900 ($150 each)</t>
   </si>
   <si>
     <t>Rezenerate Nanofacial</t>
@@ -2386,18 +2380,18 @@
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" t="s" s="9">
+      <c r="A6" t="s" s="6">
         <v>43</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="11">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="E6" s="11">
         <v>60</v>
       </c>
-      <c r="F6" t="s" s="12">
+      <c r="F6" t="s" s="9">
         <v>44</v>
       </c>
     </row>
@@ -2408,28 +2402,28 @@
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="E7" s="11">
-        <v>55</v>
-      </c>
-      <c r="F7" t="s" s="12">
+        <v>60</v>
+      </c>
+      <c r="F7" t="s" s="9">
         <v>46</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" t="s" s="6">
+      <c r="A8" t="s" s="9">
         <v>47</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="11">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="E8" s="11">
         <v>60</v>
       </c>
-      <c r="F8" t="s" s="9">
+      <c r="F8" t="s" s="12">
         <v>48</v>
       </c>
     </row>
@@ -2440,12 +2434,12 @@
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="11">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="E9" s="11">
-        <v>60</v>
-      </c>
-      <c r="F9" t="s" s="9">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s" s="12">
         <v>50</v>
       </c>
     </row>
@@ -2555,7 +2549,7 @@
         <v>185</v>
       </c>
       <c r="E16" s="11">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s" s="9">
         <v>64</v>
@@ -2567,17 +2561,17 @@
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="11">
-        <v>525</v>
+      <c r="D17" t="s" s="9">
+        <v>66</v>
       </c>
       <c r="E17" s="11">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F17" s="10"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" t="s" s="6">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -2600,7 +2594,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="5" width="14.5" style="16" customWidth="1"/>
@@ -2610,7 +2604,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s" s="2">
         <v>1</v>
@@ -2625,33 +2619,33 @@
         <v>4</v>
       </c>
       <c r="F1" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" ht="332.85" customHeight="1">
       <c r="A2" s="18"/>
       <c r="B2" t="s" s="19">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" t="s" s="20">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2" s="5">
         <v>55</v>
       </c>
       <c r="F2" t="s" s="21">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" ht="78.85" customHeight="1">
       <c r="A3" s="18"/>
       <c r="B3" t="s" s="19">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="18"/>
       <c r="D3" t="s" s="20">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" s="5">
         <v>55</v>
@@ -2661,30 +2655,30 @@
     <row r="4" ht="332.85" customHeight="1">
       <c r="A4" s="18"/>
       <c r="B4" t="s" s="6">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" t="s" s="20">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E4" s="5">
         <v>60</v>
       </c>
       <c r="F4" t="s" s="21">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" t="s" s="6">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" t="s" s="20">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E5" s="5">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s" s="6">
         <v>79</v>
@@ -2697,7 +2691,7 @@
       </c>
       <c r="C6" s="3"/>
       <c r="D6" t="s" s="20">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E6" s="5">
         <v>55</v>
@@ -2713,14 +2707,12 @@
       </c>
       <c r="C7" s="3"/>
       <c r="D7" t="s" s="20">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E7" s="5">
         <v>55</v>
       </c>
-      <c r="F7" t="s" s="6">
-        <v>83</v>
-      </c>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="3"/>
@@ -2734,55 +2726,41 @@
       <c r="E8" s="5">
         <v>55</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" t="s" s="6">
+        <v>86</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" t="s" s="6">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" t="s" s="20">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" s="5">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s" s="6">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="3"/>
-      <c r="B10" t="s" s="6">
-        <v>89</v>
-      </c>
+      <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" t="s" s="20">
-        <v>90</v>
-      </c>
-      <c r="E10" s="5">
-        <v>75</v>
-      </c>
-      <c r="F10" t="s" s="6">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
+      <c r="D10" s="23"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" ht="13.65" customHeight="1">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="23"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-    </row>
-    <row r="12" ht="13.65" customHeight="1">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2804,7 +2782,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s" s="2">
         <v>1</v>
@@ -2822,10 +2800,10 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" t="s" s="6">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s" s="6">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D2" s="5">
         <v>120</v>
@@ -2837,7 +2815,7 @@
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" t="s" s="6">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="5">
@@ -2850,7 +2828,7 @@
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" t="s" s="6">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="5">
@@ -2863,7 +2841,7 @@
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" t="s" s="6">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="5">
@@ -2876,7 +2854,7 @@
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" t="s" s="6">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="5">
@@ -2889,7 +2867,7 @@
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" t="s" s="6">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="5">
@@ -2902,7 +2880,7 @@
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" t="s" s="6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="5">
@@ -2915,7 +2893,7 @@
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" t="s" s="6">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="5">
@@ -2928,7 +2906,7 @@
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" t="s" s="6">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="5">

--- a/spreadsheets/pricing.xlsx
+++ b/spreadsheets/pricing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="99">
   <si>
     <t>WAX</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Chin</t>
   </si>
   <si>
-    <t>Ears</t>
-  </si>
-  <si>
     <t>Full Arm</t>
   </si>
   <si>
@@ -87,9 +84,6 @@
   </si>
   <si>
     <t>Lower Leg</t>
-  </si>
-  <si>
-    <t>Feet &amp; Toes</t>
   </si>
   <si>
     <t>Bikini</t>
@@ -222,7 +216,7 @@
     <t>*NEW* Exosome+V Renewal Oxygen Facial</t>
   </si>
   <si>
-    <t xml:space="preserve">An advanced post-nano microneedling treatment featuring Intraceuticals’ Exosome+V Serum, infused with vegan biomimetic exosomes, vitamins A, C &amp; E, green tea extract, bioactive peptides, and low-weight hyaluronic acid to support skin communication, renewal, and long-term skin vitality. </t>
+    <t>An advanced post-nano microneedling treatment featuring Intraceuticals’ Exosome+V Serum, infused with vegan biomimetic exosomes, vitamins A, C &amp; E, green tea extract, bioactive peptides, and low-weight hyaluronic acid to support skin communication, renewal, and long-term skin vitality. Finished with LED light therapy to further support skin renewal and recovery.</t>
   </si>
   <si>
     <t>Mona's Glow Facial</t>
@@ -235,20 +229,6 @@
   </si>
   <si>
     <t>A European facial with the addition of Sothys Lactic Acid Peel that resurfaces superficial lines and stimulates cell rejuvenation and brightening. Followed by a manual extraction and Mona's unique signature massage. Topping the treatment with a soothing ampule and Sothys W+ Illuminating Mask to complete this non-irritating acid treatment.</t>
-  </si>
-  <si>
-    <t>Detox Energie</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Detox Energie is an intensive detoxifying energizing treatment that gives the skin a burst of energy, helping it defend itself against environmental stress which can accelerate skin aging. Detox Energie is a six step treatment of intense detoxifying, exfoliation, antipollution protection, oxygenation of the skin using Digi-Esthétique Massage rebalancing, and detox using ingredients such as Elderberry, Siberian Ginseng, Peptides, Marshmallow extract, Vitamin C, and Marine complex, leaving the skin energized and radiant!
-</t>
-    </r>
   </si>
   <si>
     <t>Organic Certified Radiance Treatment by Sothys Organics®</t>
@@ -269,6 +249,20 @@
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Detox Energie</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color indexed="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">Detox Energie is an intensive detoxifying energizing treatment that gives the skin a burst of energy, helping it defend itself against environmental stress which can accelerate skin aging. Detox Energie is a six step treatment of intense detoxifying, exfoliation, antipollution protection, oxygenation of the skin using Digi-Esthétique Massage rebalancing, and detox using ingredients such as Elderberry, Siberian Ginseng, Peptides, Marshmallow extract, Vitamin C, and Marine complex, leaving the skin energized and radiant!
 </t>
     </r>
   </si>
@@ -1739,7 +1733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="9" width="14.5" style="1" customWidth="1"/>
@@ -1961,10 +1955,10 @@
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="5">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E13" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -1978,10 +1972,10 @@
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="5">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E14" s="5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -2012,10 +2006,10 @@
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="5">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E16" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -2029,10 +2023,10 @@
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="5">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="E17" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -2046,10 +2040,10 @@
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="5">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="E18" s="5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -2063,7 +2057,7 @@
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="5">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
@@ -2097,10 +2091,10 @@
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="5">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E21" s="5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -2114,10 +2108,10 @@
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="5">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E22" s="5">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -2131,10 +2125,10 @@
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="5">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E23" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -2148,10 +2142,10 @@
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="5">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E24" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -2165,10 +2159,10 @@
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="5">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="E25" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -2182,10 +2176,10 @@
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="5">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E26" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -2194,12 +2188,10 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3"/>
-      <c r="B27" t="s" s="4">
-        <v>30</v>
-      </c>
+      <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="5">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E27" s="5">
         <v>15</v>
@@ -2209,18 +2201,12 @@
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" ht="13.65" customHeight="1">
       <c r="A28" s="3"/>
-      <c r="B28" t="s" s="4">
-        <v>31</v>
-      </c>
+      <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="5">
-        <v>18</v>
-      </c>
-      <c r="E28" s="5">
-        <v>10</v>
-      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -2230,18 +2216,16 @@
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="5">
-        <v>30</v>
-      </c>
-      <c r="E29" s="5">
-        <v>15</v>
-      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-    </row>
-    <row r="30" ht="13.65" customHeight="1">
+      <c r="I29" t="s" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -2250,32 +2234,8 @@
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" t="s" s="6">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" t="s" s="6">
-        <v>33</v>
+      <c r="I30" t="s" s="6">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2299,7 +2259,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="s" s="8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s" s="8">
         <v>1</v>
@@ -2319,7 +2279,7 @@
     </row>
     <row r="2" ht="191.95" customHeight="1">
       <c r="A2" t="s" s="9">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -2330,17 +2290,17 @@
         <v>90</v>
       </c>
       <c r="F2" t="s" s="12">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" t="s" s="9">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" t="s" s="9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E3" s="11">
         <v>90</v>
@@ -2349,7 +2309,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" t="s" s="9">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -2360,12 +2320,12 @@
         <v>90</v>
       </c>
       <c r="F4" t="s" s="14">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" t="s" s="15">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -2376,12 +2336,12 @@
         <v>90</v>
       </c>
       <c r="F5" t="s" s="14">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" t="s" s="6">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -2392,12 +2352,12 @@
         <v>60</v>
       </c>
       <c r="F6" t="s" s="9">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" t="s" s="6">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -2408,44 +2368,44 @@
         <v>60</v>
       </c>
       <c r="F7" t="s" s="9">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" t="s" s="9">
-        <v>47</v>
+      <c r="A8" t="s" s="6">
+        <v>45</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="11">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="E8" s="11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s" s="12">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" t="s" s="6">
-        <v>49</v>
+      <c r="A9" t="s" s="9">
+        <v>47</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="11">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="E9" s="11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s" s="12">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" t="s" s="6">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -2456,12 +2416,12 @@
         <v>60</v>
       </c>
       <c r="F10" t="s" s="9">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" t="s" s="6">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -2472,12 +2432,12 @@
         <v>70</v>
       </c>
       <c r="F11" t="s" s="12">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" t="s" s="6">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -2488,12 +2448,12 @@
         <v>30</v>
       </c>
       <c r="F12" t="s" s="12">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" t="s" s="6">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -2504,12 +2464,12 @@
         <v>70</v>
       </c>
       <c r="F13" t="s" s="12">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" t="s" s="6">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -2520,12 +2480,12 @@
         <v>60</v>
       </c>
       <c r="F14" t="s" s="12">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" t="s" s="6">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -2536,12 +2496,12 @@
         <v>45</v>
       </c>
       <c r="F15" t="s" s="12">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" t="s" s="6">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -2552,17 +2512,17 @@
         <v>60</v>
       </c>
       <c r="F16" t="s" s="9">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" t="s" s="6">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" t="s" s="9">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E17" s="11">
         <v>60</v>
@@ -2571,7 +2531,7 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" t="s" s="6">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -2604,7 +2564,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s" s="2">
         <v>1</v>
@@ -2619,33 +2579,33 @@
         <v>4</v>
       </c>
       <c r="F1" t="s" s="2">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" ht="332.85" customHeight="1">
       <c r="A2" s="18"/>
       <c r="B2" t="s" s="19">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" t="s" s="20">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" s="5">
         <v>55</v>
       </c>
       <c r="F2" t="s" s="21">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" ht="78.85" customHeight="1">
       <c r="A3" s="18"/>
       <c r="B3" t="s" s="19">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C3" s="18"/>
       <c r="D3" t="s" s="20">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E3" s="5">
         <v>55</v>
@@ -2655,59 +2615,59 @@
     <row r="4" ht="332.85" customHeight="1">
       <c r="A4" s="18"/>
       <c r="B4" t="s" s="6">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" t="s" s="20">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E4" s="5">
         <v>60</v>
       </c>
       <c r="F4" t="s" s="21">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" t="s" s="6">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" t="s" s="20">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" s="5">
         <v>55</v>
       </c>
       <c r="F5" t="s" s="6">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" t="s" s="6">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" t="s" s="20">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E6" s="5">
         <v>55</v>
       </c>
       <c r="F6" t="s" s="6">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" t="s" s="6">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" t="s" s="20">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E7" s="5">
         <v>55</v>
@@ -2717,33 +2677,33 @@
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" t="s" s="6">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" t="s" s="20">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E8" s="5">
         <v>55</v>
       </c>
       <c r="F8" t="s" s="6">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" t="s" s="6">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" t="s" s="20">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E9" s="5">
         <v>75</v>
       </c>
       <c r="F9" t="s" s="6">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -2782,7 +2742,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B1" t="s" s="2">
         <v>1</v>
@@ -2800,10 +2760,10 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" t="s" s="6">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s" s="6">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D2" s="5">
         <v>120</v>
@@ -2815,7 +2775,7 @@
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" t="s" s="6">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="5">
@@ -2828,7 +2788,7 @@
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" t="s" s="6">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="5">
@@ -2841,7 +2801,7 @@
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" t="s" s="6">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="5">
@@ -2854,7 +2814,7 @@
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" t="s" s="6">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="5">
@@ -2867,7 +2827,7 @@
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" t="s" s="6">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="5">
@@ -2880,7 +2840,7 @@
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" t="s" s="6">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="5">
@@ -2893,7 +2853,7 @@
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" t="s" s="6">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="5">
@@ -2906,7 +2866,7 @@
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" t="s" s="6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="5">
